--- a/Scoreboard.xlsx
+++ b/Scoreboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\old\work_files\CrossFit\2026 halloween games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D1966F-9A64-4A10-B0B0-97D61E71ADE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9399E162-69C0-4183-B681-A1196AA20376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20544" yWindow="0" windowWidth="20832" windowHeight="16656" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
   </bookViews>
@@ -797,40 +797,6 @@
         <f>H2+I2+J2</f>
         <v>193</v>
       </c>
-      <c r="L2">
-        <v>10</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>63</v>
-      </c>
-      <c r="O2">
-        <v>59</v>
-      </c>
-      <c r="P2">
-        <f>N2+O2</f>
-        <v>122</v>
-      </c>
-      <c r="Q2">
-        <v>10</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>107</v>
-      </c>
-      <c r="T2">
-        <v>7</v>
-      </c>
-      <c r="U2">
-        <v>25</v>
-      </c>
-      <c r="V2">
-        <v>400</v>
-      </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -867,31 +833,6 @@
         <f t="shared" ref="K3:K37" si="0">H3+I3+J3</f>
         <v>171</v>
       </c>
-      <c r="L3">
-        <v>10</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>54</v>
-      </c>
-      <c r="O3">
-        <v>50</v>
-      </c>
-      <c r="P3">
-        <f>N3+O3</f>
-        <v>104</v>
-      </c>
-      <c r="Q3">
-        <v>7</v>
-      </c>
-      <c r="R3">
-        <v>20</v>
-      </c>
-      <c r="S3">
-        <v>120</v>
-      </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -928,31 +869,6 @@
         <f t="shared" si="0"/>
         <v>174</v>
       </c>
-      <c r="L4">
-        <v>10</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>36</v>
-      </c>
-      <c r="O4">
-        <v>57</v>
-      </c>
-      <c r="P4">
-        <f>N4+O4</f>
-        <v>93</v>
-      </c>
-      <c r="Q4">
-        <v>8</v>
-      </c>
-      <c r="R4">
-        <v>13</v>
-      </c>
-      <c r="S4">
-        <v>120</v>
-      </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -989,31 +905,6 @@
         <f t="shared" si="0"/>
         <v>191</v>
       </c>
-      <c r="L5">
-        <v>10</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>62</v>
-      </c>
-      <c r="O5">
-        <v>52</v>
-      </c>
-      <c r="P5">
-        <f>N5+O5</f>
-        <v>114</v>
-      </c>
-      <c r="Q5">
-        <v>10</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>116</v>
-      </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -1050,31 +941,6 @@
         <f t="shared" si="0"/>
         <v>183</v>
       </c>
-      <c r="L6">
-        <v>10</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>51</v>
-      </c>
-      <c r="O6">
-        <v>55</v>
-      </c>
-      <c r="P6">
-        <f>N6+O6</f>
-        <v>106</v>
-      </c>
-      <c r="Q6">
-        <v>9</v>
-      </c>
-      <c r="R6">
-        <v>34</v>
-      </c>
-      <c r="S6">
-        <v>120</v>
-      </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -1111,40 +977,6 @@
         <f t="shared" si="0"/>
         <v>175</v>
       </c>
-      <c r="L7">
-        <v>10</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>44</v>
-      </c>
-      <c r="O7">
-        <v>64</v>
-      </c>
-      <c r="P7">
-        <f>N7+O7</f>
-        <v>108</v>
-      </c>
-      <c r="Q7">
-        <v>7</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>120</v>
-      </c>
-      <c r="T7">
-        <v>9</v>
-      </c>
-      <c r="U7">
-        <v>56</v>
-      </c>
-      <c r="V7">
-        <v>400</v>
-      </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -1181,40 +1013,6 @@
         <f t="shared" si="0"/>
         <v>180</v>
       </c>
-      <c r="L8">
-        <v>10</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>49</v>
-      </c>
-      <c r="O8">
-        <v>80</v>
-      </c>
-      <c r="P8">
-        <f>N8+O8</f>
-        <v>129</v>
-      </c>
-      <c r="Q8">
-        <v>9</v>
-      </c>
-      <c r="R8">
-        <v>7</v>
-      </c>
-      <c r="S8">
-        <v>120</v>
-      </c>
-      <c r="T8">
-        <v>10</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>372</v>
-      </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -1251,31 +1049,6 @@
         <f t="shared" si="0"/>
         <v>183</v>
       </c>
-      <c r="L9">
-        <v>10</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>79</v>
-      </c>
-      <c r="O9">
-        <v>55</v>
-      </c>
-      <c r="P9">
-        <f>N9+O9</f>
-        <v>134</v>
-      </c>
-      <c r="Q9">
-        <v>10</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>83</v>
-      </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -1312,31 +1085,6 @@
         <f t="shared" si="0"/>
         <v>176</v>
       </c>
-      <c r="L10">
-        <v>10</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>55</v>
-      </c>
-      <c r="O10">
-        <v>58</v>
-      </c>
-      <c r="P10">
-        <f>N10+O10</f>
-        <v>113</v>
-      </c>
-      <c r="Q10">
-        <v>9</v>
-      </c>
-      <c r="R10">
-        <v>4</v>
-      </c>
-      <c r="S10">
-        <v>120</v>
-      </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -1373,31 +1121,6 @@
         <f t="shared" si="0"/>
         <v>165</v>
       </c>
-      <c r="L11">
-        <v>10</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>70</v>
-      </c>
-      <c r="O11">
-        <v>36</v>
-      </c>
-      <c r="P11">
-        <f>N11+O11</f>
-        <v>106</v>
-      </c>
-      <c r="Q11">
-        <v>9</v>
-      </c>
-      <c r="R11">
-        <v>39</v>
-      </c>
-      <c r="S11">
-        <v>120</v>
-      </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -1434,31 +1157,6 @@
         <f t="shared" si="0"/>
         <v>158</v>
       </c>
-      <c r="L12">
-        <v>10</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>48</v>
-      </c>
-      <c r="O12">
-        <v>41</v>
-      </c>
-      <c r="P12">
-        <f>N12+O12</f>
-        <v>89</v>
-      </c>
-      <c r="Q12">
-        <v>7</v>
-      </c>
-      <c r="R12">
-        <v>35</v>
-      </c>
-      <c r="S12">
-        <v>120</v>
-      </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -1495,31 +1193,6 @@
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
-      <c r="L13">
-        <v>10</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>60</v>
-      </c>
-      <c r="O13">
-        <v>55</v>
-      </c>
-      <c r="P13">
-        <f>N13+O13</f>
-        <v>115</v>
-      </c>
-      <c r="Q13">
-        <v>9</v>
-      </c>
-      <c r="R13">
-        <v>52</v>
-      </c>
-      <c r="S13">
-        <v>120</v>
-      </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1556,31 +1229,6 @@
         <f t="shared" si="0"/>
         <v>179</v>
       </c>
-      <c r="L14">
-        <v>10</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>71</v>
-      </c>
-      <c r="O14">
-        <v>36</v>
-      </c>
-      <c r="P14">
-        <f>N14+O14</f>
-        <v>107</v>
-      </c>
-      <c r="Q14">
-        <v>9</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>120</v>
-      </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -1617,31 +1265,6 @@
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
-      <c r="L15">
-        <v>10</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>44</v>
-      </c>
-      <c r="O15">
-        <v>76</v>
-      </c>
-      <c r="P15">
-        <f>N15+O15</f>
-        <v>120</v>
-      </c>
-      <c r="Q15">
-        <v>8</v>
-      </c>
-      <c r="R15">
-        <v>37</v>
-      </c>
-      <c r="S15">
-        <v>120</v>
-      </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -1678,33 +1301,8 @@
         <f t="shared" si="0"/>
         <v>153</v>
       </c>
-      <c r="L16">
-        <v>10</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>38</v>
-      </c>
-      <c r="O16">
-        <v>44</v>
-      </c>
-      <c r="P16">
-        <f>N16+O16</f>
-        <v>82</v>
-      </c>
-      <c r="Q16">
-        <v>10</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -1739,42 +1337,8 @@
         <f t="shared" si="0"/>
         <v>203</v>
       </c>
-      <c r="L17">
-        <v>10</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>67</v>
-      </c>
-      <c r="O17">
-        <v>58</v>
-      </c>
-      <c r="P17">
-        <f>N17+O17</f>
-        <v>125</v>
-      </c>
-      <c r="Q17">
-        <v>8</v>
-      </c>
-      <c r="R17">
-        <v>9</v>
-      </c>
-      <c r="S17">
-        <v>120</v>
-      </c>
-      <c r="T17">
-        <v>9</v>
-      </c>
-      <c r="U17">
-        <v>9</v>
-      </c>
-      <c r="V17">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -1809,33 +1373,8 @@
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
-      <c r="L18">
-        <v>10</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>63</v>
-      </c>
-      <c r="O18">
-        <v>82</v>
-      </c>
-      <c r="P18">
-        <f>N18+O18</f>
-        <v>145</v>
-      </c>
-      <c r="Q18">
-        <v>10</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -1870,33 +1409,8 @@
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
-      <c r="L19">
-        <v>10</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>45</v>
-      </c>
-      <c r="O19">
-        <v>67</v>
-      </c>
-      <c r="P19">
-        <f>N19+O19</f>
-        <v>112</v>
-      </c>
-      <c r="Q19">
-        <v>8</v>
-      </c>
-      <c r="R19">
-        <v>55</v>
-      </c>
-      <c r="S19">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -1931,42 +1445,8 @@
         <f t="shared" si="0"/>
         <v>208</v>
       </c>
-      <c r="L20">
-        <v>10</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>50</v>
-      </c>
-      <c r="O20">
-        <v>63</v>
-      </c>
-      <c r="P20">
-        <f>N20+O20</f>
-        <v>113</v>
-      </c>
-      <c r="Q20">
-        <v>9</v>
-      </c>
-      <c r="R20">
-        <v>3</v>
-      </c>
-      <c r="S20">
-        <v>120</v>
-      </c>
-      <c r="T20">
-        <v>10</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -2001,42 +1481,8 @@
         <f t="shared" si="0"/>
         <v>214</v>
       </c>
-      <c r="L21">
-        <v>10</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>82</v>
-      </c>
-      <c r="O21">
-        <v>76</v>
-      </c>
-      <c r="P21">
-        <f>N21+O21</f>
-        <v>158</v>
-      </c>
-      <c r="Q21">
-        <v>9</v>
-      </c>
-      <c r="R21">
-        <v>23</v>
-      </c>
-      <c r="S21">
-        <v>120</v>
-      </c>
-      <c r="T21">
-        <v>8</v>
-      </c>
-      <c r="U21">
-        <v>14</v>
-      </c>
-      <c r="V21">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -2071,42 +1517,8 @@
         <f t="shared" si="0"/>
         <v>199</v>
       </c>
-      <c r="L22">
-        <v>10</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>62</v>
-      </c>
-      <c r="O22">
-        <v>72</v>
-      </c>
-      <c r="P22">
-        <f>N22+O22</f>
-        <v>134</v>
-      </c>
-      <c r="Q22">
-        <v>7</v>
-      </c>
-      <c r="R22">
-        <v>22</v>
-      </c>
-      <c r="S22">
-        <v>120</v>
-      </c>
-      <c r="T22">
-        <v>9</v>
-      </c>
-      <c r="U22">
-        <v>45</v>
-      </c>
-      <c r="V22">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -2141,33 +1553,8 @@
         <f t="shared" si="0"/>
         <v>202</v>
       </c>
-      <c r="L23">
-        <v>10</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>54</v>
-      </c>
-      <c r="O23">
-        <v>47</v>
-      </c>
-      <c r="P23">
-        <f>N23+O23</f>
-        <v>101</v>
-      </c>
-      <c r="Q23">
-        <v>10</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -2202,33 +1589,8 @@
         <f t="shared" si="0"/>
         <v>188</v>
       </c>
-      <c r="L24">
-        <v>10</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
-        <v>51</v>
-      </c>
-      <c r="O24">
-        <v>38</v>
-      </c>
-      <c r="P24">
-        <f>N24+O24</f>
-        <v>89</v>
-      </c>
-      <c r="Q24">
-        <v>9</v>
-      </c>
-      <c r="R24">
-        <v>35</v>
-      </c>
-      <c r="S24">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -2263,42 +1625,8 @@
         <f t="shared" si="0"/>
         <v>194</v>
       </c>
-      <c r="L25">
-        <v>10</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>78</v>
-      </c>
-      <c r="O25">
-        <v>68</v>
-      </c>
-      <c r="P25">
-        <f>N25+O25</f>
-        <v>146</v>
-      </c>
-      <c r="Q25">
-        <v>7</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>120</v>
-      </c>
-      <c r="T25">
-        <v>10</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
-      <c r="V25">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -2333,42 +1661,8 @@
         <f t="shared" si="0"/>
         <v>186</v>
       </c>
-      <c r="L26">
-        <v>10</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <v>38</v>
-      </c>
-      <c r="O26">
-        <v>84</v>
-      </c>
-      <c r="P26">
-        <f>N26+O26</f>
-        <v>122</v>
-      </c>
-      <c r="Q26">
-        <v>10</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>108</v>
-      </c>
-      <c r="T26">
-        <v>7</v>
-      </c>
-      <c r="U26">
-        <v>46</v>
-      </c>
-      <c r="V26">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -2403,33 +1697,8 @@
         <f t="shared" si="0"/>
         <v>148</v>
       </c>
-      <c r="L27">
-        <v>10</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27">
-        <v>77</v>
-      </c>
-      <c r="O27">
-        <v>56</v>
-      </c>
-      <c r="P27">
-        <f>N27+O27</f>
-        <v>133</v>
-      </c>
-      <c r="Q27">
-        <v>10</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -2464,33 +1733,8 @@
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
-      <c r="L28">
-        <v>10</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>49</v>
-      </c>
-      <c r="O28">
-        <v>59</v>
-      </c>
-      <c r="P28">
-        <f>N28+O28</f>
-        <v>108</v>
-      </c>
-      <c r="Q28">
-        <v>8</v>
-      </c>
-      <c r="R28">
-        <v>22</v>
-      </c>
-      <c r="S28">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -2525,42 +1769,8 @@
         <f t="shared" si="0"/>
         <v>192</v>
       </c>
-      <c r="L29">
-        <v>10</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29">
-        <v>52</v>
-      </c>
-      <c r="O29">
-        <v>66</v>
-      </c>
-      <c r="P29">
-        <f>N29+O29</f>
-        <v>118</v>
-      </c>
-      <c r="Q29">
-        <v>8</v>
-      </c>
-      <c r="R29">
-        <v>52</v>
-      </c>
-      <c r="S29">
-        <v>120</v>
-      </c>
-      <c r="T29">
-        <v>9</v>
-      </c>
-      <c r="U29">
-        <v>40</v>
-      </c>
-      <c r="V29">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -2595,33 +1805,8 @@
         <f t="shared" si="0"/>
         <v>169</v>
       </c>
-      <c r="L30">
-        <v>10</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>67</v>
-      </c>
-      <c r="O30">
-        <v>59</v>
-      </c>
-      <c r="P30">
-        <f>N30+O30</f>
-        <v>126</v>
-      </c>
-      <c r="Q30">
-        <v>9</v>
-      </c>
-      <c r="R30">
-        <v>37</v>
-      </c>
-      <c r="S30">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -2656,33 +1841,8 @@
         <f t="shared" si="0"/>
         <v>170</v>
       </c>
-      <c r="L31">
-        <v>10</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>65</v>
-      </c>
-      <c r="O31">
-        <v>54</v>
-      </c>
-      <c r="P31">
-        <f>N31+O31</f>
-        <v>119</v>
-      </c>
-      <c r="Q31">
-        <v>9</v>
-      </c>
-      <c r="R31">
-        <v>31</v>
-      </c>
-      <c r="S31">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>76</v>
       </c>
@@ -2717,42 +1877,8 @@
         <f t="shared" si="0"/>
         <v>185</v>
       </c>
-      <c r="L32">
-        <v>10</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>83</v>
-      </c>
-      <c r="O32">
-        <v>58</v>
-      </c>
-      <c r="P32">
-        <f>N32+O32</f>
-        <v>141</v>
-      </c>
-      <c r="Q32">
-        <v>8</v>
-      </c>
-      <c r="R32">
-        <v>1</v>
-      </c>
-      <c r="S32">
-        <v>120</v>
-      </c>
-      <c r="T32">
-        <v>8</v>
-      </c>
-      <c r="U32">
-        <v>19</v>
-      </c>
-      <c r="V32">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>78</v>
       </c>
@@ -2787,42 +1913,8 @@
         <f t="shared" si="0"/>
         <v>186</v>
       </c>
-      <c r="L33">
-        <v>10</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>75.5</v>
-      </c>
-      <c r="O33">
-        <v>83</v>
-      </c>
-      <c r="P33">
-        <f>N33+O33</f>
-        <v>158.5</v>
-      </c>
-      <c r="Q33">
-        <v>7</v>
-      </c>
-      <c r="R33">
-        <v>58</v>
-      </c>
-      <c r="S33">
-        <v>120</v>
-      </c>
-      <c r="T33">
-        <v>10</v>
-      </c>
-      <c r="U33">
-        <v>0</v>
-      </c>
-      <c r="V33">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>80</v>
       </c>
@@ -2857,33 +1949,8 @@
         <f t="shared" si="0"/>
         <v>180</v>
       </c>
-      <c r="L34">
-        <v>10</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>42</v>
-      </c>
-      <c r="O34">
-        <v>69</v>
-      </c>
-      <c r="P34">
-        <f>N34+O34</f>
-        <v>111</v>
-      </c>
-      <c r="Q34">
-        <v>10</v>
-      </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -2918,33 +1985,8 @@
         <f t="shared" si="0"/>
         <v>167</v>
       </c>
-      <c r="L35">
-        <v>10</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <v>42</v>
-      </c>
-      <c r="O35">
-        <v>47</v>
-      </c>
-      <c r="P35">
-        <f>N35+O35</f>
-        <v>89</v>
-      </c>
-      <c r="Q35">
-        <v>10</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>84</v>
       </c>
@@ -2979,33 +2021,8 @@
         <f t="shared" si="0"/>
         <v>157</v>
       </c>
-      <c r="L36">
-        <v>10</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>58</v>
-      </c>
-      <c r="O36">
-        <v>72</v>
-      </c>
-      <c r="P36">
-        <f>N36+O36</f>
-        <v>130</v>
-      </c>
-      <c r="Q36">
-        <v>8</v>
-      </c>
-      <c r="R36">
-        <v>46</v>
-      </c>
-      <c r="S36">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>86</v>
       </c>
@@ -3039,31 +2056,6 @@
       <c r="K37">
         <f t="shared" si="0"/>
         <v>214</v>
-      </c>
-      <c r="L37">
-        <v>10</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37">
-        <v>52</v>
-      </c>
-      <c r="O37">
-        <v>44</v>
-      </c>
-      <c r="P37">
-        <f>N37+O37</f>
-        <v>96</v>
-      </c>
-      <c r="Q37">
-        <v>10</v>
-      </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
-        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/Scoreboard.xlsx
+++ b/Scoreboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\old\work_files\CrossFit\2026 halloween games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9399E162-69C0-4183-B681-A1196AA20376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4946BB60-07B6-4D9A-8C95-898618F622FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20544" yWindow="0" windowWidth="20832" windowHeight="16656" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
   </bookViews>
   <sheets>
     <sheet name="Score" sheetId="1" r:id="rId1"/>
@@ -769,34 +769,6 @@
       <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="C2">
-        <v>7</v>
-      </c>
-      <c r="D2">
-        <v>12</v>
-      </c>
-      <c r="E2">
-        <v>1260</v>
-      </c>
-      <c r="F2">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>53</v>
-      </c>
-      <c r="I2">
-        <v>60</v>
-      </c>
-      <c r="J2">
-        <v>80</v>
-      </c>
-      <c r="K2">
-        <f>H2+I2+J2</f>
-        <v>193</v>
-      </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -805,34 +777,6 @@
       <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>1213</v>
-      </c>
-      <c r="F3">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>64</v>
-      </c>
-      <c r="I3">
-        <v>63</v>
-      </c>
-      <c r="J3">
-        <v>44</v>
-      </c>
-      <c r="K3">
-        <f t="shared" ref="K3:K37" si="0">H3+I3+J3</f>
-        <v>171</v>
-      </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -841,34 +785,6 @@
       <c r="B4" t="s">
         <v>21</v>
       </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>1240</v>
-      </c>
-      <c r="F4">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>46</v>
-      </c>
-      <c r="I4">
-        <v>77</v>
-      </c>
-      <c r="J4">
-        <v>51</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="0"/>
-        <v>174</v>
-      </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -877,34 +793,6 @@
       <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="C5">
-        <v>8</v>
-      </c>
-      <c r="D5">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>1260</v>
-      </c>
-      <c r="F5">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>47</v>
-      </c>
-      <c r="I5">
-        <v>72</v>
-      </c>
-      <c r="J5">
-        <v>72</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="0"/>
-        <v>191</v>
-      </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -913,34 +801,6 @@
       <c r="B6" t="s">
         <v>25</v>
       </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>1214</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>38</v>
-      </c>
-      <c r="I6">
-        <v>80</v>
-      </c>
-      <c r="J6">
-        <v>65</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="0"/>
-        <v>183</v>
-      </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -949,34 +809,6 @@
       <c r="B7" t="s">
         <v>27</v>
       </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>17</v>
-      </c>
-      <c r="E7">
-        <v>1260</v>
-      </c>
-      <c r="F7">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>71</v>
-      </c>
-      <c r="I7">
-        <v>58</v>
-      </c>
-      <c r="J7">
-        <v>46</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="0"/>
-        <v>175</v>
-      </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -985,34 +817,6 @@
       <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="C8">
-        <v>8</v>
-      </c>
-      <c r="D8">
-        <v>15</v>
-      </c>
-      <c r="E8">
-        <v>1260</v>
-      </c>
-      <c r="F8">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>43</v>
-      </c>
-      <c r="I8">
-        <v>58</v>
-      </c>
-      <c r="J8">
-        <v>79</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="0"/>
-        <v>180</v>
-      </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -1021,34 +825,6 @@
       <c r="B9" t="s">
         <v>31</v>
       </c>
-      <c r="C9">
-        <v>10</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>1228</v>
-      </c>
-      <c r="F9">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>58</v>
-      </c>
-      <c r="I9">
-        <v>52</v>
-      </c>
-      <c r="J9">
-        <v>73</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="0"/>
-        <v>183</v>
-      </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -1057,34 +833,6 @@
       <c r="B10" t="s">
         <v>33</v>
       </c>
-      <c r="C10">
-        <v>10</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>1211</v>
-      </c>
-      <c r="F10">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>45</v>
-      </c>
-      <c r="I10">
-        <v>78</v>
-      </c>
-      <c r="J10">
-        <v>53</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="0"/>
-        <v>176</v>
-      </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -1093,34 +841,6 @@
       <c r="B11" t="s">
         <v>35</v>
       </c>
-      <c r="C11">
-        <v>9</v>
-      </c>
-      <c r="D11">
-        <v>57</v>
-      </c>
-      <c r="E11">
-        <v>1260</v>
-      </c>
-      <c r="F11">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>32</v>
-      </c>
-      <c r="I11">
-        <v>78</v>
-      </c>
-      <c r="J11">
-        <v>55</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="0"/>
-        <v>165</v>
-      </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -1129,34 +849,6 @@
       <c r="B12" t="s">
         <v>37</v>
       </c>
-      <c r="C12">
-        <v>7</v>
-      </c>
-      <c r="D12">
-        <v>58</v>
-      </c>
-      <c r="E12">
-        <v>1260</v>
-      </c>
-      <c r="F12">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>53</v>
-      </c>
-      <c r="I12">
-        <v>49</v>
-      </c>
-      <c r="J12">
-        <v>56</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="0"/>
-        <v>158</v>
-      </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -1165,34 +857,6 @@
       <c r="B13" t="s">
         <v>39</v>
       </c>
-      <c r="C13">
-        <v>8</v>
-      </c>
-      <c r="D13">
-        <v>27</v>
-      </c>
-      <c r="E13">
-        <v>1260</v>
-      </c>
-      <c r="F13">
-        <v>11</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>63</v>
-      </c>
-      <c r="I13">
-        <v>45</v>
-      </c>
-      <c r="J13">
-        <v>48</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="0"/>
-        <v>156</v>
-      </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1201,34 +865,6 @@
       <c r="B14" t="s">
         <v>41</v>
       </c>
-      <c r="C14">
-        <v>10</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>1222</v>
-      </c>
-      <c r="F14">
-        <v>11</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>38</v>
-      </c>
-      <c r="I14">
-        <v>82</v>
-      </c>
-      <c r="J14">
-        <v>59</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="0"/>
-        <v>179</v>
-      </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -1237,34 +873,6 @@
       <c r="B15" t="s">
         <v>43</v>
       </c>
-      <c r="C15">
-        <v>10</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>1217</v>
-      </c>
-      <c r="F15">
-        <v>11</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>29</v>
-      </c>
-      <c r="I15">
-        <v>70</v>
-      </c>
-      <c r="J15">
-        <v>43</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="0"/>
-        <v>142</v>
-      </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -1273,789 +881,173 @@
       <c r="B16" t="s">
         <v>45</v>
       </c>
-      <c r="C16">
-        <v>8</v>
-      </c>
-      <c r="D16">
-        <v>41</v>
-      </c>
-      <c r="E16">
-        <v>1260</v>
-      </c>
-      <c r="F16">
-        <v>11</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>45</v>
-      </c>
-      <c r="I16">
-        <v>56</v>
-      </c>
-      <c r="J16">
-        <v>52</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="0"/>
-        <v>153</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>46</v>
       </c>
       <c r="B17" t="s">
         <v>47</v>
       </c>
-      <c r="C17">
-        <v>10</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>1247</v>
-      </c>
-      <c r="F17">
-        <v>11</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>53</v>
-      </c>
-      <c r="I17">
-        <v>74</v>
-      </c>
-      <c r="J17">
-        <v>76</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="0"/>
-        <v>203</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>48</v>
       </c>
       <c r="B18" t="s">
         <v>49</v>
       </c>
-      <c r="C18">
-        <v>9</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>1260</v>
-      </c>
-      <c r="F18">
-        <v>11</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>52</v>
-      </c>
-      <c r="I18">
-        <v>63</v>
-      </c>
-      <c r="J18">
-        <v>49</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="0"/>
-        <v>164</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>50</v>
       </c>
       <c r="B19" t="s">
         <v>51</v>
       </c>
-      <c r="C19">
-        <v>10</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>1252</v>
-      </c>
-      <c r="F19">
-        <v>11</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>29</v>
-      </c>
-      <c r="I19">
-        <v>79</v>
-      </c>
-      <c r="J19">
-        <v>56</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="0"/>
-        <v>164</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>52</v>
       </c>
       <c r="B20" t="s">
         <v>53</v>
       </c>
-      <c r="C20">
-        <v>7</v>
-      </c>
-      <c r="D20">
-        <v>40</v>
-      </c>
-      <c r="E20">
-        <v>1260</v>
-      </c>
-      <c r="F20">
-        <v>11</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>40</v>
-      </c>
-      <c r="I20">
-        <v>90</v>
-      </c>
-      <c r="J20">
-        <v>78</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="0"/>
-        <v>208</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>54</v>
       </c>
       <c r="B21" t="s">
         <v>55</v>
       </c>
-      <c r="C21">
-        <v>9</v>
-      </c>
-      <c r="D21">
-        <v>5</v>
-      </c>
-      <c r="E21">
-        <v>1260</v>
-      </c>
-      <c r="F21">
-        <v>11</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>71</v>
-      </c>
-      <c r="I21">
-        <v>91</v>
-      </c>
-      <c r="J21">
-        <v>52</v>
-      </c>
-      <c r="K21">
-        <f t="shared" si="0"/>
-        <v>214</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>56</v>
       </c>
       <c r="B22" t="s">
         <v>57</v>
       </c>
-      <c r="C22">
-        <v>10</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>1251</v>
-      </c>
-      <c r="F22">
-        <v>11</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>55</v>
-      </c>
-      <c r="I22">
-        <v>93</v>
-      </c>
-      <c r="J22">
-        <v>51</v>
-      </c>
-      <c r="K22">
-        <f t="shared" si="0"/>
-        <v>199</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>58</v>
       </c>
       <c r="B23" t="s">
         <v>59</v>
       </c>
-      <c r="C23">
-        <v>9</v>
-      </c>
-      <c r="D23">
-        <v>19</v>
-      </c>
-      <c r="E23">
-        <v>1260</v>
-      </c>
-      <c r="F23">
-        <v>11</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>58</v>
-      </c>
-      <c r="I23">
-        <v>67</v>
-      </c>
-      <c r="J23">
-        <v>77</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="0"/>
-        <v>202</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>60</v>
       </c>
       <c r="B24" t="s">
         <v>61</v>
       </c>
-      <c r="C24">
-        <v>8</v>
-      </c>
-      <c r="D24">
-        <v>24</v>
-      </c>
-      <c r="E24">
-        <v>1260</v>
-      </c>
-      <c r="F24">
-        <v>11</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>62</v>
-      </c>
-      <c r="I24">
-        <v>84</v>
-      </c>
-      <c r="J24">
-        <v>42</v>
-      </c>
-      <c r="K24">
-        <f t="shared" si="0"/>
-        <v>188</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>62</v>
       </c>
       <c r="B25" t="s">
         <v>63</v>
       </c>
-      <c r="C25">
-        <v>7</v>
-      </c>
-      <c r="D25">
-        <v>10</v>
-      </c>
-      <c r="E25">
-        <v>1260</v>
-      </c>
-      <c r="F25">
-        <v>11</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>55</v>
-      </c>
-      <c r="I25">
-        <v>82</v>
-      </c>
-      <c r="J25">
-        <v>57</v>
-      </c>
-      <c r="K25">
-        <f t="shared" si="0"/>
-        <v>194</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>64</v>
       </c>
       <c r="B26" t="s">
         <v>65</v>
       </c>
-      <c r="C26">
-        <v>7</v>
-      </c>
-      <c r="D26">
-        <v>41</v>
-      </c>
-      <c r="E26">
-        <v>1260</v>
-      </c>
-      <c r="F26">
-        <v>11</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>50</v>
-      </c>
-      <c r="I26">
-        <v>86</v>
-      </c>
-      <c r="J26">
-        <v>50</v>
-      </c>
-      <c r="K26">
-        <f t="shared" si="0"/>
-        <v>186</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>66</v>
       </c>
       <c r="B27" t="s">
         <v>67</v>
       </c>
-      <c r="C27">
-        <v>8</v>
-      </c>
-      <c r="D27">
-        <v>15</v>
-      </c>
-      <c r="E27">
-        <v>1260</v>
-      </c>
-      <c r="F27">
-        <v>11</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>35</v>
-      </c>
-      <c r="I27">
-        <v>65</v>
-      </c>
-      <c r="J27">
-        <v>48</v>
-      </c>
-      <c r="K27">
-        <f t="shared" si="0"/>
-        <v>148</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>68</v>
       </c>
       <c r="B28" t="s">
         <v>69</v>
       </c>
-      <c r="C28">
-        <v>9</v>
-      </c>
-      <c r="D28">
-        <v>23</v>
-      </c>
-      <c r="E28">
-        <v>1260</v>
-      </c>
-      <c r="F28">
-        <v>11</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>26</v>
-      </c>
-      <c r="I28">
-        <v>48</v>
-      </c>
-      <c r="J28">
-        <v>56</v>
-      </c>
-      <c r="K28">
-        <f t="shared" si="0"/>
-        <v>130</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>70</v>
       </c>
       <c r="B29" t="s">
         <v>71</v>
       </c>
-      <c r="C29">
-        <v>9</v>
-      </c>
-      <c r="D29">
-        <v>4</v>
-      </c>
-      <c r="E29">
-        <v>1260</v>
-      </c>
-      <c r="F29">
-        <v>11</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>48</v>
-      </c>
-      <c r="I29">
-        <v>73</v>
-      </c>
-      <c r="J29">
-        <v>71</v>
-      </c>
-      <c r="K29">
-        <f t="shared" si="0"/>
-        <v>192</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>72</v>
       </c>
       <c r="B30" t="s">
         <v>73</v>
       </c>
-      <c r="C30">
-        <v>9</v>
-      </c>
-      <c r="D30">
-        <v>46</v>
-      </c>
-      <c r="E30">
-        <v>1260</v>
-      </c>
-      <c r="F30">
-        <v>11</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>41</v>
-      </c>
-      <c r="I30">
-        <v>49</v>
-      </c>
-      <c r="J30">
-        <v>79</v>
-      </c>
-      <c r="K30">
-        <f t="shared" si="0"/>
-        <v>169</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>74</v>
       </c>
       <c r="B31" t="s">
         <v>75</v>
       </c>
-      <c r="C31">
-        <v>10</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31">
-        <v>1229</v>
-      </c>
-      <c r="F31">
-        <v>11</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>40</v>
-      </c>
-      <c r="I31">
-        <v>70</v>
-      </c>
-      <c r="J31">
-        <v>60</v>
-      </c>
-      <c r="K31">
-        <f t="shared" si="0"/>
-        <v>170</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>76</v>
       </c>
       <c r="B32" t="s">
         <v>77</v>
       </c>
-      <c r="C32">
-        <v>7</v>
-      </c>
-      <c r="D32">
-        <v>6</v>
-      </c>
-      <c r="E32">
-        <v>1260</v>
-      </c>
-      <c r="F32">
-        <v>11</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>72</v>
-      </c>
-      <c r="I32">
-        <v>46</v>
-      </c>
-      <c r="J32">
-        <v>67</v>
-      </c>
-      <c r="K32">
-        <f t="shared" si="0"/>
-        <v>185</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>78</v>
       </c>
       <c r="B33" t="s">
         <v>79</v>
       </c>
-      <c r="C33">
-        <v>7</v>
-      </c>
-      <c r="D33">
-        <v>10</v>
-      </c>
-      <c r="E33">
-        <v>1260</v>
-      </c>
-      <c r="F33">
-        <v>11</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>32</v>
-      </c>
-      <c r="I33">
-        <v>90</v>
-      </c>
-      <c r="J33">
-        <v>64</v>
-      </c>
-      <c r="K33">
-        <f t="shared" si="0"/>
-        <v>186</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>80</v>
       </c>
       <c r="B34" t="s">
         <v>81</v>
       </c>
-      <c r="C34">
-        <v>9</v>
-      </c>
-      <c r="D34">
-        <v>13</v>
-      </c>
-      <c r="E34">
-        <v>1260</v>
-      </c>
-      <c r="F34">
-        <v>11</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>62</v>
-      </c>
-      <c r="I34">
-        <v>53</v>
-      </c>
-      <c r="J34">
-        <v>65</v>
-      </c>
-      <c r="K34">
-        <f t="shared" si="0"/>
-        <v>180</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>82</v>
       </c>
       <c r="B35" t="s">
         <v>83</v>
       </c>
-      <c r="C35">
-        <v>10</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35">
-        <v>1258</v>
-      </c>
-      <c r="F35">
-        <v>11</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>36</v>
-      </c>
-      <c r="I35">
-        <v>67</v>
-      </c>
-      <c r="J35">
-        <v>64</v>
-      </c>
-      <c r="K35">
-        <f t="shared" si="0"/>
-        <v>167</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>84</v>
       </c>
       <c r="B36" t="s">
         <v>85</v>
       </c>
-      <c r="C36">
-        <v>8</v>
-      </c>
-      <c r="D36">
-        <v>39</v>
-      </c>
-      <c r="E36">
-        <v>1260</v>
-      </c>
-      <c r="F36">
-        <v>11</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>29</v>
-      </c>
-      <c r="I36">
-        <v>69</v>
-      </c>
-      <c r="J36">
-        <v>59</v>
-      </c>
-      <c r="K36">
-        <f t="shared" si="0"/>
-        <v>157</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>86</v>
       </c>
       <c r="B37" t="s">
         <v>87</v>
-      </c>
-      <c r="C37">
-        <v>9</v>
-      </c>
-      <c r="D37">
-        <v>30</v>
-      </c>
-      <c r="E37">
-        <v>1260</v>
-      </c>
-      <c r="F37">
-        <v>11</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>61</v>
-      </c>
-      <c r="I37">
-        <v>78</v>
-      </c>
-      <c r="J37">
-        <v>75</v>
-      </c>
-      <c r="K37">
-        <f t="shared" si="0"/>
-        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/Scoreboard.xlsx
+++ b/Scoreboard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\old\work_files\CrossFit\2026 halloween games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4946BB60-07B6-4D9A-8C95-898618F622FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F90A95-DC5C-4C80-ACE6-DB1B0A6A174B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
   </bookViews>
   <sheets>
     <sheet name="Score" sheetId="1" r:id="rId1"/>
@@ -185,9 +185,6 @@
     <t>David og Åshild</t>
   </si>
   <si>
-    <t>Nothing Beats a Jet2 Workout Of the Day</t>
-  </si>
-  <si>
     <t>Daniel og Maria</t>
   </si>
   <si>
@@ -324,6 +321,9 @@
   </si>
   <si>
     <t>Rep5</t>
+  </si>
+  <si>
+    <t>Nothing Beats a Jet2 WOD</t>
   </si>
 </sst>
 </file>
@@ -717,13 +717,13 @@
         <v>5</v>
       </c>
       <c r="H1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" t="s">
         <v>88</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>89</v>
-      </c>
-      <c r="J1" t="s">
-        <v>90</v>
       </c>
       <c r="K1" t="s">
         <v>12</v>
@@ -735,10 +735,10 @@
         <v>7</v>
       </c>
       <c r="N1" t="s">
+        <v>90</v>
+      </c>
+      <c r="O1" t="s">
         <v>91</v>
-      </c>
-      <c r="O1" t="s">
-        <v>92</v>
       </c>
       <c r="P1" t="s">
         <v>8</v>
@@ -753,301 +753,364 @@
         <v>13</v>
       </c>
       <c r="T1" t="s">
+        <v>92</v>
+      </c>
+      <c r="U1" t="s">
         <v>93</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>94</v>
-      </c>
-      <c r="V1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>64</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>1240</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>56</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>1248</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>33</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>1000</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1247</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>1197</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>1195</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>1259</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Scoreboard.xlsx
+++ b/Scoreboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\old\work_files\CrossFit\2026 halloween games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F90A95-DC5C-4C80-ACE6-DB1B0A6A174B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5B4DEC-DA6E-43E7-9EA5-5909522D22CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
   </bookViews>
@@ -883,239 +883,302 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>1256</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>43</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>1247</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>52</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>1251</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="C12">
+        <v>9</v>
+      </c>
+      <c r="D12">
+        <v>56</v>
+      </c>
+      <c r="E12">
+        <v>1260</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>84</v>
+      </c>
+      <c r="C13">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>1205</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>58</v>
+      </c>
+      <c r="C14">
+        <v>9</v>
+      </c>
+      <c r="D14">
+        <v>11</v>
+      </c>
+      <c r="E14">
+        <v>1260</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>37</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>1254</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="B29" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B21">
-    <sortCondition ref="B2:B21"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B15">
+    <sortCondition ref="B2:B15"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Scoreboard.xlsx
+++ b/Scoreboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\old\work_files\CrossFit\2026 halloween games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5B4DEC-DA6E-43E7-9EA5-5909522D22CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{752FF0CE-9DF2-474C-9DAE-DB1A0DBD1FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
   </bookViews>
@@ -1007,56 +1007,119 @@
       <c r="B16" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C16">
+        <v>9</v>
+      </c>
+      <c r="D16">
+        <v>22</v>
+      </c>
+      <c r="E16">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>49</v>
       </c>
       <c r="B17" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C17">
+        <v>10</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>46</v>
       </c>
       <c r="B18" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C18">
+        <v>10</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>61</v>
       </c>
       <c r="B19" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C19">
+        <v>10</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>48</v>
       </c>
       <c r="B20" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C20">
+        <v>10</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>40</v>
       </c>
       <c r="B21" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C21">
+        <v>9</v>
+      </c>
+      <c r="D21">
+        <v>53</v>
+      </c>
+      <c r="E21">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
       <c r="B22" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C22">
+        <v>9</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -1064,7 +1127,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>85</v>
       </c>
@@ -1072,7 +1135,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -1080,7 +1143,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -1088,7 +1151,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>69</v>
       </c>
@@ -1096,7 +1159,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>73</v>
       </c>
@@ -1104,7 +1167,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>81</v>
       </c>
@@ -1112,7 +1175,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>20</v>
       </c>
@@ -1120,7 +1183,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>75</v>
       </c>
@@ -1128,7 +1191,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>38</v>
       </c>

--- a/Scoreboard.xlsx
+++ b/Scoreboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\old\work_files\CrossFit\2026 halloween games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{752FF0CE-9DF2-474C-9DAE-DB1A0DBD1FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96DCDB97-455A-4FDF-A9F4-43A772409532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
   </bookViews>
@@ -912,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>1247</v>
+        <v>1247.01</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
@@ -1048,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>1254</v>
+        <v>1254.01</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1126,6 +1126,15 @@
       <c r="B23" t="s">
         <v>17</v>
       </c>
+      <c r="C23">
+        <v>9</v>
+      </c>
+      <c r="D23">
+        <v>38.1</v>
+      </c>
+      <c r="E23">
+        <v>1260</v>
+      </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -1134,6 +1143,15 @@
       <c r="B24" t="s">
         <v>86</v>
       </c>
+      <c r="C24">
+        <v>8</v>
+      </c>
+      <c r="D24">
+        <v>33</v>
+      </c>
+      <c r="E24">
+        <v>1260</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -1142,6 +1160,15 @@
       <c r="B25" t="s">
         <v>72</v>
       </c>
+      <c r="C25">
+        <v>9</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25">
+        <v>1260</v>
+      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -1150,6 +1177,15 @@
       <c r="B26" t="s">
         <v>66</v>
       </c>
+      <c r="C26">
+        <v>8</v>
+      </c>
+      <c r="D26">
+        <v>5</v>
+      </c>
+      <c r="E26">
+        <v>1260</v>
+      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
@@ -1158,6 +1194,15 @@
       <c r="B27" t="s">
         <v>70</v>
       </c>
+      <c r="C27">
+        <v>9</v>
+      </c>
+      <c r="D27">
+        <v>38</v>
+      </c>
+      <c r="E27">
+        <v>1260</v>
+      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -1166,6 +1211,15 @@
       <c r="B28" t="s">
         <v>74</v>
       </c>
+      <c r="C28">
+        <v>9</v>
+      </c>
+      <c r="D28">
+        <v>7</v>
+      </c>
+      <c r="E28">
+        <v>1260</v>
+      </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -1174,6 +1228,15 @@
       <c r="B29" t="s">
         <v>82</v>
       </c>
+      <c r="C29">
+        <v>8</v>
+      </c>
+      <c r="D29">
+        <v>23</v>
+      </c>
+      <c r="E29">
+        <v>1260</v>
+      </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -1181,6 +1244,15 @@
       </c>
       <c r="B30" t="s">
         <v>21</v>
+      </c>
+      <c r="C30">
+        <v>9</v>
+      </c>
+      <c r="D30">
+        <v>15</v>
+      </c>
+      <c r="E30">
+        <v>1260</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">

--- a/Scoreboard.xlsx
+++ b/Scoreboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\old\work_files\CrossFit\2026 halloween games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96DCDB97-455A-4FDF-A9F4-43A772409532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC7B257-C089-4357-A526-1BF7BC27758A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
   </bookViews>
@@ -1065,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>1258</v>
+        <v>1258.01</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1262,6 +1262,15 @@
       <c r="B31" t="s">
         <v>76</v>
       </c>
+      <c r="C31">
+        <v>9</v>
+      </c>
+      <c r="D31">
+        <v>16</v>
+      </c>
+      <c r="E31">
+        <v>1260</v>
+      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -1270,45 +1279,99 @@
       <c r="B32" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C32">
+        <v>9</v>
+      </c>
+      <c r="D32">
+        <v>36</v>
+      </c>
+      <c r="E32">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>67</v>
       </c>
       <c r="B33" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C33">
+        <v>9</v>
+      </c>
+      <c r="D33">
+        <v>45</v>
+      </c>
+      <c r="E33">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>34</v>
       </c>
       <c r="B34" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C34">
+        <v>10</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>1253.01</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>77</v>
       </c>
       <c r="B35" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C35">
+        <v>9</v>
+      </c>
+      <c r="D35">
+        <v>42</v>
+      </c>
+      <c r="E35">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>53</v>
       </c>
       <c r="B36" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C36">
+        <v>10</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>79</v>
       </c>
       <c r="B37" t="s">
         <v>80</v>
+      </c>
+      <c r="C37">
+        <v>10</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>1240.01</v>
       </c>
     </row>
   </sheetData>

--- a/Scoreboard.xlsx
+++ b/Scoreboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\old\work_files\CrossFit\2026 halloween games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC7B257-C089-4357-A526-1BF7BC27758A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04EC9B28-2C49-42F2-BF76-F76F40C41005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
   </bookViews>
@@ -778,6 +778,25 @@
       <c r="E2">
         <v>1240</v>
       </c>
+      <c r="F2">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>42</v>
+      </c>
+      <c r="I2">
+        <v>53</v>
+      </c>
+      <c r="J2">
+        <v>63</v>
+      </c>
+      <c r="K2">
+        <f>H2+I2+J2</f>
+        <v>158</v>
+      </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -795,6 +814,25 @@
       <c r="E3">
         <v>1248</v>
       </c>
+      <c r="F3">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>55</v>
+      </c>
+      <c r="I3">
+        <v>117</v>
+      </c>
+      <c r="J3">
+        <v>92</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K37" si="0">H3+I3+J3</f>
+        <v>264</v>
+      </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -812,6 +850,25 @@
       <c r="E4">
         <v>1000</v>
       </c>
+      <c r="F4">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -829,6 +886,25 @@
       <c r="E5">
         <v>1247</v>
       </c>
+      <c r="F5">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>70</v>
+      </c>
+      <c r="I5">
+        <v>99</v>
+      </c>
+      <c r="J5">
+        <v>93</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="0"/>
+        <v>262</v>
+      </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -846,6 +922,25 @@
       <c r="E6">
         <v>1197</v>
       </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>75</v>
+      </c>
+      <c r="I6">
+        <v>101</v>
+      </c>
+      <c r="J6">
+        <v>82</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="0"/>
+        <v>258</v>
+      </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -863,6 +958,25 @@
       <c r="E7">
         <v>1195</v>
       </c>
+      <c r="F7">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>35</v>
+      </c>
+      <c r="I7">
+        <v>86</v>
+      </c>
+      <c r="J7">
+        <v>70</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="0"/>
+        <v>191</v>
+      </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -880,6 +994,25 @@
       <c r="E8">
         <v>1259</v>
       </c>
+      <c r="F8">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>59</v>
+      </c>
+      <c r="I8">
+        <v>110</v>
+      </c>
+      <c r="J8">
+        <v>102</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>271</v>
+      </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -897,6 +1030,25 @@
       <c r="E9">
         <v>1256</v>
       </c>
+      <c r="F9">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>68</v>
+      </c>
+      <c r="I9">
+        <v>101</v>
+      </c>
+      <c r="J9">
+        <v>99</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="0"/>
+        <v>268</v>
+      </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -914,6 +1066,25 @@
       <c r="E10">
         <v>1247.01</v>
       </c>
+      <c r="F10">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>44</v>
+      </c>
+      <c r="I10">
+        <v>113</v>
+      </c>
+      <c r="J10">
+        <v>90</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="0"/>
+        <v>247</v>
+      </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -931,6 +1102,25 @@
       <c r="E11">
         <v>1251</v>
       </c>
+      <c r="F11">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>60</v>
+      </c>
+      <c r="I11">
+        <v>114</v>
+      </c>
+      <c r="J11">
+        <v>97</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>271</v>
+      </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -948,6 +1138,25 @@
       <c r="E12">
         <v>1260</v>
       </c>
+      <c r="F12">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>63</v>
+      </c>
+      <c r="I12">
+        <v>118</v>
+      </c>
+      <c r="J12">
+        <v>98</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="0"/>
+        <v>279</v>
+      </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -965,6 +1174,25 @@
       <c r="E13">
         <v>1205</v>
       </c>
+      <c r="F13">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>34</v>
+      </c>
+      <c r="I13">
+        <v>87</v>
+      </c>
+      <c r="J13">
+        <v>86</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="0"/>
+        <v>207</v>
+      </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -982,6 +1210,25 @@
       <c r="E14">
         <v>1260</v>
       </c>
+      <c r="F14">
+        <v>11</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>63</v>
+      </c>
+      <c r="I14">
+        <v>105</v>
+      </c>
+      <c r="J14">
+        <v>97</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>265</v>
+      </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -999,6 +1246,25 @@
       <c r="E15">
         <v>1254</v>
       </c>
+      <c r="F15">
+        <v>11</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>80</v>
+      </c>
+      <c r="I15">
+        <v>110</v>
+      </c>
+      <c r="J15">
+        <v>97</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>287</v>
+      </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -1016,8 +1282,27 @@
       <c r="E16">
         <v>1260</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>72</v>
+      </c>
+      <c r="I16">
+        <v>111</v>
+      </c>
+      <c r="J16">
+        <v>99</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="0"/>
+        <v>282</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -1033,8 +1318,27 @@
       <c r="E17">
         <v>1253</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>62</v>
+      </c>
+      <c r="I17">
+        <v>102</v>
+      </c>
+      <c r="J17">
+        <v>97</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="0"/>
+        <v>261</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1050,8 +1354,27 @@
       <c r="E18">
         <v>1254.01</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18">
+        <v>11</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>90</v>
+      </c>
+      <c r="I18">
+        <v>107</v>
+      </c>
+      <c r="J18">
+        <v>105</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="0"/>
+        <v>302</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -1067,8 +1390,27 @@
       <c r="E19">
         <v>1258.01</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19">
+        <v>11</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>67</v>
+      </c>
+      <c r="I19">
+        <v>122</v>
+      </c>
+      <c r="J19">
+        <v>97</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="0"/>
+        <v>286</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1084,8 +1426,27 @@
       <c r="E20">
         <v>1252</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F20">
+        <v>11</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>43</v>
+      </c>
+      <c r="I20">
+        <v>110</v>
+      </c>
+      <c r="J20">
+        <v>87</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -1101,8 +1462,27 @@
       <c r="E21">
         <v>1260</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F21">
+        <v>11</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>85</v>
+      </c>
+      <c r="I21">
+        <v>115</v>
+      </c>
+      <c r="J21">
+        <v>99</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="0"/>
+        <v>299</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -1118,8 +1498,27 @@
       <c r="E22">
         <v>1260</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F22">
+        <v>11</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>76</v>
+      </c>
+      <c r="I22">
+        <v>125</v>
+      </c>
+      <c r="J22">
+        <v>103</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="0"/>
+        <v>304</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -1135,8 +1534,27 @@
       <c r="E23">
         <v>1260</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F23">
+        <v>11</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>87</v>
+      </c>
+      <c r="I23">
+        <v>107</v>
+      </c>
+      <c r="J23">
+        <v>100</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="0"/>
+        <v>294</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>85</v>
       </c>
@@ -1152,8 +1570,27 @@
       <c r="E24">
         <v>1260</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F24">
+        <v>11</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>103</v>
+      </c>
+      <c r="I24">
+        <v>125</v>
+      </c>
+      <c r="J24">
+        <v>97</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="0"/>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -1169,8 +1606,27 @@
       <c r="E25">
         <v>1260</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F25">
+        <v>11</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>85</v>
+      </c>
+      <c r="I25">
+        <v>110</v>
+      </c>
+      <c r="J25">
+        <v>107</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="0"/>
+        <v>302</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -1186,8 +1642,27 @@
       <c r="E26">
         <v>1260</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F26">
+        <v>11</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>102</v>
+      </c>
+      <c r="I26">
+        <v>147</v>
+      </c>
+      <c r="J26">
+        <v>109</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="0"/>
+        <v>358</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>69</v>
       </c>
@@ -1203,8 +1678,27 @@
       <c r="E27">
         <v>1260</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F27">
+        <v>11</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>94</v>
+      </c>
+      <c r="I27">
+        <v>112</v>
+      </c>
+      <c r="J27">
+        <v>91</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="0"/>
+        <v>297</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>73</v>
       </c>
@@ -1220,8 +1714,27 @@
       <c r="E28">
         <v>1260</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F28">
+        <v>11</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>90</v>
+      </c>
+      <c r="I28">
+        <v>118</v>
+      </c>
+      <c r="J28">
+        <v>97</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="0"/>
+        <v>305</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>81</v>
       </c>
@@ -1237,8 +1750,27 @@
       <c r="E29">
         <v>1260</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F29">
+        <v>11</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>105</v>
+      </c>
+      <c r="I29">
+        <v>122</v>
+      </c>
+      <c r="J29">
+        <v>107</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="0"/>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>20</v>
       </c>
@@ -1254,8 +1786,27 @@
       <c r="E30">
         <v>1260</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F30">
+        <v>11</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>75</v>
+      </c>
+      <c r="I30">
+        <v>119</v>
+      </c>
+      <c r="J30">
+        <v>93</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="0"/>
+        <v>287</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>75</v>
       </c>
@@ -1271,8 +1822,27 @@
       <c r="E31">
         <v>1260</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F31">
+        <v>11</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>92</v>
+      </c>
+      <c r="I31">
+        <v>117</v>
+      </c>
+      <c r="J31">
+        <v>65</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="0"/>
+        <v>274</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>38</v>
       </c>
@@ -1288,8 +1858,27 @@
       <c r="E32">
         <v>1260</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F32">
+        <v>11</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>95</v>
+      </c>
+      <c r="I32">
+        <v>111</v>
+      </c>
+      <c r="J32">
+        <v>98</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="0"/>
+        <v>304</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1305,8 +1894,27 @@
       <c r="E33">
         <v>1260</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F33">
+        <v>11</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>90</v>
+      </c>
+      <c r="I33">
+        <v>116</v>
+      </c>
+      <c r="J33">
+        <v>97</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="0"/>
+        <v>303</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -1322,8 +1930,27 @@
       <c r="E34">
         <v>1253.01</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F34">
+        <v>11</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>74</v>
+      </c>
+      <c r="I34">
+        <v>106</v>
+      </c>
+      <c r="J34">
+        <v>99</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="0"/>
+        <v>279</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>77</v>
       </c>
@@ -1339,8 +1966,27 @@
       <c r="E35">
         <v>1260</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F35">
+        <v>11</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>68</v>
+      </c>
+      <c r="I35">
+        <v>119</v>
+      </c>
+      <c r="J35">
+        <v>103</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="0"/>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>53</v>
       </c>
@@ -1356,8 +2002,27 @@
       <c r="E36">
         <v>1258</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F36">
+        <v>11</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>89</v>
+      </c>
+      <c r="I36">
+        <v>102</v>
+      </c>
+      <c r="J36">
+        <v>95</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="0"/>
+        <v>286</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>79</v>
       </c>
@@ -1372,6 +2037,25 @@
       </c>
       <c r="E37">
         <v>1240.01</v>
+      </c>
+      <c r="F37">
+        <v>11</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>65</v>
+      </c>
+      <c r="I37">
+        <v>94</v>
+      </c>
+      <c r="J37">
+        <v>85</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="0"/>
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/Scoreboard.xlsx
+++ b/Scoreboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\old\work_files\CrossFit\2026 halloween games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04EC9B28-2C49-42F2-BF76-F76F40C41005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FDDCCD-78B8-4009-B2E8-F97787BD3252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
   </bookViews>
@@ -797,6 +797,31 @@
         <f>H2+I2+J2</f>
         <v>158</v>
       </c>
+      <c r="L2">
+        <v>10</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>107.5</v>
+      </c>
+      <c r="O2">
+        <v>75</v>
+      </c>
+      <c r="P2">
+        <f>N2+O2</f>
+        <v>182.5</v>
+      </c>
+      <c r="Q2">
+        <v>5</v>
+      </c>
+      <c r="R2">
+        <v>36</v>
+      </c>
+      <c r="S2">
+        <v>120</v>
+      </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -833,6 +858,31 @@
         <f t="shared" ref="K3:K37" si="0">H3+I3+J3</f>
         <v>264</v>
       </c>
+      <c r="L3">
+        <v>10</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>65</v>
+      </c>
+      <c r="O3">
+        <v>80</v>
+      </c>
+      <c r="P3">
+        <f t="shared" ref="P3:P37" si="1">N3+O3</f>
+        <v>145</v>
+      </c>
+      <c r="Q3">
+        <v>5</v>
+      </c>
+      <c r="R3">
+        <v>24</v>
+      </c>
+      <c r="S3">
+        <v>120</v>
+      </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -869,6 +919,31 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="L4">
+        <v>10</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -905,6 +980,31 @@
         <f t="shared" si="0"/>
         <v>262</v>
       </c>
+      <c r="L5">
+        <v>10</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>67.5</v>
+      </c>
+      <c r="O5">
+        <v>90</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="1"/>
+        <v>157.5</v>
+      </c>
+      <c r="Q5">
+        <v>5</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>120</v>
+      </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -941,6 +1041,31 @@
         <f t="shared" si="0"/>
         <v>258</v>
       </c>
+      <c r="L6">
+        <v>10</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>105</v>
+      </c>
+      <c r="O6">
+        <v>70</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="1"/>
+        <v>175</v>
+      </c>
+      <c r="Q6">
+        <v>5</v>
+      </c>
+      <c r="R6">
+        <v>56</v>
+      </c>
+      <c r="S6">
+        <v>120</v>
+      </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -977,6 +1102,31 @@
         <f t="shared" si="0"/>
         <v>191</v>
       </c>
+      <c r="L7">
+        <v>10</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>102.5</v>
+      </c>
+      <c r="O7">
+        <v>50</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="1"/>
+        <v>152.5</v>
+      </c>
+      <c r="Q7">
+        <v>9</v>
+      </c>
+      <c r="R7">
+        <v>15</v>
+      </c>
+      <c r="S7">
+        <v>120</v>
+      </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -1013,6 +1163,31 @@
         <f t="shared" si="0"/>
         <v>271</v>
       </c>
+      <c r="L8">
+        <v>10</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>107.5</v>
+      </c>
+      <c r="O8">
+        <v>62.5</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="1"/>
+        <v>170</v>
+      </c>
+      <c r="Q8">
+        <v>5</v>
+      </c>
+      <c r="R8">
+        <v>42</v>
+      </c>
+      <c r="S8">
+        <v>120</v>
+      </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -1049,6 +1224,16 @@
         <f t="shared" si="0"/>
         <v>268</v>
       </c>
+      <c r="L9">
+        <v>10</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -1085,6 +1270,16 @@
         <f t="shared" si="0"/>
         <v>247</v>
       </c>
+      <c r="L10">
+        <v>10</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -1121,6 +1316,16 @@
         <f t="shared" si="0"/>
         <v>271</v>
       </c>
+      <c r="L11">
+        <v>10</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -1157,6 +1362,16 @@
         <f t="shared" si="0"/>
         <v>279</v>
       </c>
+      <c r="L12">
+        <v>10</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -1193,6 +1408,16 @@
         <f t="shared" si="0"/>
         <v>207</v>
       </c>
+      <c r="L13">
+        <v>10</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1229,6 +1454,16 @@
         <f t="shared" si="0"/>
         <v>265</v>
       </c>
+      <c r="L14">
+        <v>10</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -1265,6 +1500,16 @@
         <f t="shared" si="0"/>
         <v>287</v>
       </c>
+      <c r="L15">
+        <v>10</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -1301,8 +1546,18 @@
         <f t="shared" si="0"/>
         <v>282</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L16">
+        <v>10</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -1337,8 +1592,18 @@
         <f t="shared" si="0"/>
         <v>261</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L17">
+        <v>10</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1373,8 +1638,18 @@
         <f t="shared" si="0"/>
         <v>302</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L18">
+        <v>10</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -1409,8 +1684,18 @@
         <f t="shared" si="0"/>
         <v>286</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L19">
+        <v>10</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1445,8 +1730,18 @@
         <f t="shared" si="0"/>
         <v>240</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L20">
+        <v>10</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -1481,8 +1776,18 @@
         <f t="shared" si="0"/>
         <v>299</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L21">
+        <v>10</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -1517,8 +1822,18 @@
         <f t="shared" si="0"/>
         <v>304</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L22">
+        <v>10</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -1553,8 +1868,18 @@
         <f t="shared" si="0"/>
         <v>294</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L23">
+        <v>10</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>85</v>
       </c>
@@ -1589,8 +1914,18 @@
         <f t="shared" si="0"/>
         <v>325</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L24">
+        <v>10</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -1625,8 +1960,18 @@
         <f t="shared" si="0"/>
         <v>302</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L25">
+        <v>10</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -1661,8 +2006,18 @@
         <f t="shared" si="0"/>
         <v>358</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L26">
+        <v>10</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>69</v>
       </c>
@@ -1697,8 +2052,18 @@
         <f t="shared" si="0"/>
         <v>297</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L27">
+        <v>10</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>73</v>
       </c>
@@ -1733,8 +2098,18 @@
         <f t="shared" si="0"/>
         <v>305</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L28">
+        <v>10</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>81</v>
       </c>
@@ -1769,8 +2144,18 @@
         <f t="shared" si="0"/>
         <v>334</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L29">
+        <v>10</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>20</v>
       </c>
@@ -1805,8 +2190,18 @@
         <f t="shared" si="0"/>
         <v>287</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L30">
+        <v>10</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>75</v>
       </c>
@@ -1841,8 +2236,18 @@
         <f t="shared" si="0"/>
         <v>274</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L31">
+        <v>10</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>38</v>
       </c>
@@ -1877,8 +2282,18 @@
         <f t="shared" si="0"/>
         <v>304</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L32">
+        <v>10</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1913,8 +2328,18 @@
         <f t="shared" si="0"/>
         <v>303</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L33">
+        <v>10</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -1949,8 +2374,18 @@
         <f t="shared" si="0"/>
         <v>279</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L34">
+        <v>10</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>77</v>
       </c>
@@ -1985,8 +2420,18 @@
         <f t="shared" si="0"/>
         <v>290</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L35">
+        <v>10</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>53</v>
       </c>
@@ -2021,8 +2466,18 @@
         <f t="shared" si="0"/>
         <v>286</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L36">
+        <v>10</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>79</v>
       </c>
@@ -2056,6 +2511,16 @@
       <c r="K37">
         <f t="shared" si="0"/>
         <v>244</v>
+      </c>
+      <c r="L37">
+        <v>10</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Scoreboard.xlsx
+++ b/Scoreboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\old\work_files\CrossFit\2026 halloween games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FDDCCD-78B8-4009-B2E8-F97787BD3252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9062DE4E-7138-4952-8E79-63B1DDB61849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
   </bookViews>
@@ -1230,9 +1230,24 @@
       <c r="M9">
         <v>0</v>
       </c>
+      <c r="N9">
+        <v>110</v>
+      </c>
+      <c r="O9">
+        <v>65</v>
+      </c>
       <c r="P9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>175</v>
+      </c>
+      <c r="Q9">
+        <v>5</v>
+      </c>
+      <c r="R9">
+        <v>42</v>
+      </c>
+      <c r="S9">
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
@@ -1276,9 +1291,24 @@
       <c r="M10">
         <v>0</v>
       </c>
+      <c r="N10">
+        <v>100</v>
+      </c>
+      <c r="O10">
+        <v>60</v>
+      </c>
       <c r="P10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>160</v>
+      </c>
+      <c r="Q10">
+        <v>6</v>
+      </c>
+      <c r="R10">
+        <v>9</v>
+      </c>
+      <c r="S10">
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
@@ -1322,9 +1352,24 @@
       <c r="M11">
         <v>0</v>
       </c>
+      <c r="N11">
+        <v>87.5</v>
+      </c>
+      <c r="O11">
+        <v>95</v>
+      </c>
       <c r="P11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>182.5</v>
+      </c>
+      <c r="Q11">
+        <v>5</v>
+      </c>
+      <c r="R11">
+        <v>46</v>
+      </c>
+      <c r="S11">
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
@@ -1368,9 +1413,24 @@
       <c r="M12">
         <v>0</v>
       </c>
+      <c r="N12">
+        <v>60</v>
+      </c>
+      <c r="O12">
+        <v>85</v>
+      </c>
       <c r="P12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>145</v>
+      </c>
+      <c r="Q12">
+        <v>5</v>
+      </c>
+      <c r="R12">
+        <v>12</v>
+      </c>
+      <c r="S12">
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
@@ -1414,9 +1474,24 @@
       <c r="M13">
         <v>0</v>
       </c>
+      <c r="N13">
+        <v>47.5</v>
+      </c>
+      <c r="O13">
+        <v>70</v>
+      </c>
       <c r="P13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>117.5</v>
+      </c>
+      <c r="Q13">
+        <v>7</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
@@ -1460,9 +1535,24 @@
       <c r="M14">
         <v>0</v>
       </c>
+      <c r="N14">
+        <v>62.5</v>
+      </c>
+      <c r="O14">
+        <v>100</v>
+      </c>
       <c r="P14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>162.5</v>
+      </c>
+      <c r="Q14">
+        <v>4</v>
+      </c>
+      <c r="R14">
+        <v>55</v>
+      </c>
+      <c r="S14">
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
@@ -1506,9 +1596,24 @@
       <c r="M15">
         <v>0</v>
       </c>
+      <c r="N15">
+        <v>47.5</v>
+      </c>
+      <c r="O15">
+        <v>125</v>
+      </c>
       <c r="P15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>172.5</v>
+      </c>
+      <c r="Q15">
+        <v>5</v>
+      </c>
+      <c r="R15">
+        <v>9</v>
+      </c>
+      <c r="S15">
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">

--- a/Scoreboard.xlsx
+++ b/Scoreboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\old\work_files\CrossFit\2026 halloween games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9062DE4E-7138-4952-8E79-63B1DDB61849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A99CD8-0B0B-415A-B92D-711DE7F56010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
   </bookViews>
@@ -1493,6 +1493,9 @@
       <c r="S13">
         <v>120</v>
       </c>
+      <c r="T13">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1657,12 +1660,27 @@
       <c r="M16">
         <v>0</v>
       </c>
+      <c r="N16">
+        <v>100</v>
+      </c>
+      <c r="O16">
+        <v>70</v>
+      </c>
       <c r="P16">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="Q16">
+        <v>5</v>
+      </c>
+      <c r="R16">
+        <v>44</v>
+      </c>
+      <c r="S16">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -1703,12 +1721,27 @@
       <c r="M17">
         <v>0</v>
       </c>
+      <c r="N17">
+        <v>72.5</v>
+      </c>
+      <c r="O17">
+        <v>105</v>
+      </c>
       <c r="P17">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+        <v>177.5</v>
+      </c>
+      <c r="Q17">
+        <v>6</v>
+      </c>
+      <c r="R17">
+        <v>4</v>
+      </c>
+      <c r="S17">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1749,12 +1782,27 @@
       <c r="M18">
         <v>0</v>
       </c>
+      <c r="N18">
+        <v>110</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
       <c r="P18">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -1795,12 +1843,27 @@
       <c r="M19">
         <v>0</v>
       </c>
+      <c r="N19">
+        <v>70</v>
+      </c>
+      <c r="O19">
+        <v>85</v>
+      </c>
       <c r="P19">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+      <c r="Q19">
+        <v>4</v>
+      </c>
+      <c r="R19">
+        <v>49</v>
+      </c>
+      <c r="S19">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1841,12 +1904,27 @@
       <c r="M20">
         <v>0</v>
       </c>
+      <c r="N20">
+        <v>45</v>
+      </c>
+      <c r="O20">
+        <v>120</v>
+      </c>
       <c r="P20">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+      <c r="Q20">
+        <v>6</v>
+      </c>
+      <c r="R20">
+        <v>10</v>
+      </c>
+      <c r="S20">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -1887,12 +1965,27 @@
       <c r="M21">
         <v>0</v>
       </c>
+      <c r="N21">
+        <v>105</v>
+      </c>
+      <c r="O21">
+        <v>70</v>
+      </c>
       <c r="P21">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+      <c r="Q21">
+        <v>4</v>
+      </c>
+      <c r="R21">
+        <v>45</v>
+      </c>
+      <c r="S21">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -1933,12 +2026,27 @@
       <c r="M22">
         <v>0</v>
       </c>
+      <c r="N22">
+        <v>140</v>
+      </c>
+      <c r="O22">
+        <v>67.5</v>
+      </c>
       <c r="P22">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+        <v>207.5</v>
+      </c>
+      <c r="Q22">
+        <v>4</v>
+      </c>
+      <c r="R22">
+        <v>27</v>
+      </c>
+      <c r="S22">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -1984,7 +2092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>85</v>
       </c>
@@ -2030,7 +2138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -2076,7 +2184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -2122,7 +2230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>69</v>
       </c>
@@ -2168,7 +2276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>73</v>
       </c>
@@ -2214,7 +2322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>81</v>
       </c>
@@ -2260,7 +2368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>20</v>
       </c>
@@ -2306,7 +2414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>75</v>
       </c>
@@ -2352,7 +2460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>38</v>
       </c>

--- a/Scoreboard.xlsx
+++ b/Scoreboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\old\work_files\CrossFit\2026 halloween games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A99CD8-0B0B-415A-B92D-711DE7F56010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FAB013-7784-4D9A-95C7-0FFDF5C018D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
   </bookViews>
@@ -2087,9 +2087,24 @@
       <c r="M23">
         <v>0</v>
       </c>
+      <c r="N23">
+        <v>130</v>
+      </c>
+      <c r="O23">
+        <v>70</v>
+      </c>
       <c r="P23">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="Q23">
+        <v>4</v>
+      </c>
+      <c r="R23">
+        <v>21</v>
+      </c>
+      <c r="S23">
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
@@ -2133,9 +2148,24 @@
       <c r="M24">
         <v>0</v>
       </c>
+      <c r="N24">
+        <v>92.5</v>
+      </c>
+      <c r="O24">
+        <v>110</v>
+      </c>
       <c r="P24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>202.5</v>
+      </c>
+      <c r="Q24">
+        <v>4</v>
+      </c>
+      <c r="R24">
+        <v>3</v>
+      </c>
+      <c r="S24">
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
@@ -2179,9 +2209,24 @@
       <c r="M25">
         <v>0</v>
       </c>
+      <c r="N25">
+        <v>125</v>
+      </c>
+      <c r="O25">
+        <v>95</v>
+      </c>
       <c r="P25">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>220</v>
+      </c>
+      <c r="Q25">
+        <v>4</v>
+      </c>
+      <c r="R25">
+        <v>20</v>
+      </c>
+      <c r="S25">
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
@@ -2225,9 +2270,24 @@
       <c r="M26">
         <v>0</v>
       </c>
+      <c r="N26">
+        <v>90</v>
+      </c>
+      <c r="O26">
+        <v>155</v>
+      </c>
       <c r="P26">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>245</v>
+      </c>
+      <c r="Q26">
+        <v>3</v>
+      </c>
+      <c r="R26">
+        <v>44</v>
+      </c>
+      <c r="S26">
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
@@ -2271,9 +2331,24 @@
       <c r="M27">
         <v>0</v>
       </c>
+      <c r="N27">
+        <v>85</v>
+      </c>
+      <c r="O27">
+        <v>115</v>
+      </c>
       <c r="P27">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="Q27">
+        <v>4</v>
+      </c>
+      <c r="R27">
+        <v>45</v>
+      </c>
+      <c r="S27">
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
@@ -2317,9 +2392,24 @@
       <c r="M28">
         <v>0</v>
       </c>
+      <c r="N28">
+        <v>80</v>
+      </c>
+      <c r="O28">
+        <v>120</v>
+      </c>
       <c r="P28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="Q28">
+        <v>4</v>
+      </c>
+      <c r="R28">
+        <v>25</v>
+      </c>
+      <c r="S28">
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
@@ -2363,9 +2453,24 @@
       <c r="M29">
         <v>0</v>
       </c>
+      <c r="N29">
+        <v>105</v>
+      </c>
+      <c r="O29">
+        <v>120</v>
+      </c>
       <c r="P29">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>225</v>
+      </c>
+      <c r="Q29">
+        <v>3</v>
+      </c>
+      <c r="R29">
+        <v>54</v>
+      </c>
+      <c r="S29">
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
@@ -2409,8 +2514,23 @@
       <c r="M30">
         <v>0</v>
       </c>
+      <c r="N30">
+        <v>165</v>
+      </c>
+      <c r="O30">
+        <v>25</v>
+      </c>
       <c r="P30">
         <f t="shared" si="1"/>
+        <v>190</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
         <v>0</v>
       </c>
     </row>

--- a/Scoreboard.xlsx
+++ b/Scoreboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\old\work_files\CrossFit\2026 halloween games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FAB013-7784-4D9A-95C7-0FFDF5C018D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF2323B6-CB0E-4A01-B1BF-C378A92EE15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
   </bookViews>
@@ -2575,9 +2575,24 @@
       <c r="M31">
         <v>0</v>
       </c>
+      <c r="N31">
+        <v>80</v>
+      </c>
+      <c r="O31">
+        <v>117.5</v>
+      </c>
       <c r="P31">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>197.5</v>
+      </c>
+      <c r="Q31">
+        <v>4</v>
+      </c>
+      <c r="R31">
+        <v>36</v>
+      </c>
+      <c r="S31">
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
@@ -2621,12 +2636,27 @@
       <c r="M32">
         <v>0</v>
       </c>
+      <c r="N32">
+        <v>102.5</v>
+      </c>
+      <c r="O32">
+        <v>80</v>
+      </c>
       <c r="P32">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+        <v>182.5</v>
+      </c>
+      <c r="Q32">
+        <v>4</v>
+      </c>
+      <c r="R32">
+        <v>30</v>
+      </c>
+      <c r="S32">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -2667,12 +2697,27 @@
       <c r="M33">
         <v>0</v>
       </c>
+      <c r="N33">
+        <v>135</v>
+      </c>
+      <c r="O33">
+        <v>90</v>
+      </c>
       <c r="P33">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+      <c r="Q33">
+        <v>4</v>
+      </c>
+      <c r="R33">
+        <v>26</v>
+      </c>
+      <c r="S33">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -2713,12 +2758,27 @@
       <c r="M34">
         <v>0</v>
       </c>
+      <c r="N34">
+        <v>60</v>
+      </c>
+      <c r="O34">
+        <v>90</v>
+      </c>
       <c r="P34">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+      <c r="Q34">
+        <v>5</v>
+      </c>
+      <c r="R34">
+        <v>27</v>
+      </c>
+      <c r="S34">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>77</v>
       </c>
@@ -2759,12 +2819,27 @@
       <c r="M35">
         <v>0</v>
       </c>
+      <c r="N35">
+        <v>90</v>
+      </c>
+      <c r="O35">
+        <v>65</v>
+      </c>
       <c r="P35">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+      <c r="Q35">
+        <v>5</v>
+      </c>
+      <c r="R35">
+        <v>23</v>
+      </c>
+      <c r="S35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>53</v>
       </c>
@@ -2805,12 +2880,27 @@
       <c r="M36">
         <v>0</v>
       </c>
+      <c r="N36">
+        <v>120</v>
+      </c>
+      <c r="O36">
+        <v>72.5</v>
+      </c>
       <c r="P36">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+        <v>192.5</v>
+      </c>
+      <c r="Q36">
+        <v>4</v>
+      </c>
+      <c r="R36">
+        <v>45</v>
+      </c>
+      <c r="S36">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>79</v>
       </c>
@@ -2851,9 +2941,24 @@
       <c r="M37">
         <v>0</v>
       </c>
+      <c r="N37">
+        <v>65</v>
+      </c>
+      <c r="O37">
+        <v>70</v>
+      </c>
       <c r="P37">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>135</v>
+      </c>
+      <c r="Q37">
+        <v>5</v>
+      </c>
+      <c r="R37">
+        <v>37</v>
+      </c>
+      <c r="S37">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Scoreboard.xlsx
+++ b/Scoreboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\old\work_files\CrossFit\2026 halloween games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF2323B6-CB0E-4A01-B1BF-C378A92EE15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF23230-040F-49CD-A256-9A31AC13B9AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{96A6929C-9832-4037-ABF1-822A6F612440}"/>
   </bookViews>
@@ -1493,9 +1493,6 @@
       <c r="S13">
         <v>120</v>
       </c>
-      <c r="T13">
-        <v>3</v>
-      </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1680,7 +1677,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -1741,7 +1738,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1802,7 +1799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -1863,7 +1860,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1924,7 +1921,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -1984,8 +1981,17 @@
       <c r="S21">
         <v>120</v>
       </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T21">
+        <v>15</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -2045,8 +2051,17 @@
       <c r="S22">
         <v>120</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T22">
+        <v>15</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -2106,8 +2121,17 @@
       <c r="S23">
         <v>120</v>
       </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T23">
+        <v>15</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>85</v>
       </c>
@@ -2167,8 +2191,17 @@
       <c r="S24">
         <v>120</v>
       </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T24">
+        <v>15</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -2228,8 +2261,17 @@
       <c r="S25">
         <v>120</v>
       </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T25">
+        <v>15</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -2289,8 +2331,17 @@
       <c r="S26">
         <v>120</v>
       </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T26">
+        <v>13</v>
+      </c>
+      <c r="U26">
+        <v>58</v>
+      </c>
+      <c r="V26">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>69</v>
       </c>
@@ -2350,8 +2401,17 @@
       <c r="S27">
         <v>120</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T27">
+        <v>15</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>73</v>
       </c>
@@ -2411,8 +2471,17 @@
       <c r="S28">
         <v>120</v>
       </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T28">
+        <v>15</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>81</v>
       </c>
@@ -2472,8 +2541,17 @@
       <c r="S29">
         <v>120</v>
       </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T29">
+        <v>12</v>
+      </c>
+      <c r="U29">
+        <v>33</v>
+      </c>
+      <c r="V29">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>20</v>
       </c>
@@ -2534,7 +2612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>75</v>
       </c>
@@ -2594,8 +2672,17 @@
       <c r="S31">
         <v>120</v>
       </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T31">
+        <v>15</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>38</v>
       </c>
@@ -2655,8 +2742,17 @@
       <c r="S32">
         <v>120</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T32">
+        <v>15</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -2716,8 +2812,17 @@
       <c r="S33">
         <v>120</v>
       </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T33">
+        <v>15</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -2778,7 +2883,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>77</v>
       </c>
@@ -2839,7 +2944,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>53</v>
       </c>
@@ -2900,7 +3005,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>79</v>
       </c>
